--- a/emergency_contact_form_templates/026_hospital_emergency_contact_form--emergency_contact_form_templates.xlsx
+++ b/emergency_contact_form_templates/026_hospital_emergency_contact_form--emergency_contact_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other_relative'}</t>
+          <t>other_relative</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other Relative'}</t>
+          <t>Other Relative</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'allergic_to_medications'}</t>
+          <t>allergic_to_medications</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Allergic to medications'}</t>
+          <t>Allergic to medications</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'heart_condition'}</t>
+          <t>heart_condition</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Heart condition'}</t>
+          <t>Heart condition</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'penicillin'}</t>
+          <t>penicillin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Penicillin'}</t>
+          <t>Penicillin</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'codeine'}</t>
+          <t>codeine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Codeine'}</t>
+          <t>Codeine</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'ibuprofen'}</t>
+          <t>ibuprofen</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Ibuprofen'}</t>
+          <t>Ibuprofen</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'nurse'}</t>
+          <t>nurse</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Nurse'}</t>
+          <t>Nurse</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
